--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260701.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260701.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>7,926,409</t>
+          <t>6,881,844</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>6,881,844</t>
+          <t>7,926,409</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>338,648,680</t>
+          <t>14,513,402</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>14,513,402</t>
+          <t>338,648,680</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>23,381,645</t>
+          <t>3,844,197</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>3,844,197</t>
+          <t>23,381,645</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
